--- a/backend/data/attachments/wealth_高端客户服务标准手册_10.xlsx
+++ b/backend/data/attachments/wealth_高端客户服务标准手册_10.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C2" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D2" t="n">
-        <v>5474</v>
+        <v>11347</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>239</v>
+        <v>496</v>
       </c>
       <c r="C3" t="n">
-        <v>459</v>
+        <v>273</v>
       </c>
       <c r="D3" t="n">
-        <v>4122</v>
+        <v>3780</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1195</v>
+        <v>1792</v>
       </c>
       <c r="C4" t="n">
-        <v>559</v>
+        <v>542</v>
       </c>
       <c r="D4" t="n">
-        <v>306</v>
+        <v>367</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="C7" t="n">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -564,14 +564,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
